--- a/Summer_2026_Semester/datasets/chili/chili.xlsx
+++ b/Summer_2026_Semester/datasets/chili/chili.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeje/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B325EE-60E6-4043-A934-81576A42D109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E91747-6DD2-0D44-9A2B-FFD848CE5530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="21140" windowHeight="14740" xr2:uid="{D42A6087-2C07-AC4F-A0AB-FE3A65267EE5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Author</t>
   </si>
@@ -81,6 +81,29 @@
   </si>
   <si>
     <t>Environmental Variability, Generalization (Domain Shift</t>
+  </si>
+  <si>
+    <t>https://www.frontiersin.org/journals/plant-science/articles/10.3389/fpls.2025.1691415/full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shtwai Alsubai,
+Ahmad Almadhor 
+Ahmad Almadhor,
+Abdullah Al Hejaili,
+Thippa Reddy Gadekallu 
+Thippa Reddy Gadekallu </t>
+  </si>
+  <si>
+    <t>ResNet-PCA and hybrid ML–DNN</t>
+  </si>
+  <si>
+    <t>frontiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dataset limitation, Environmental Variability, Domain Shift, Subtle Symptom Detection </t>
+  </si>
+  <si>
+    <t>https://github.com/spmohanty/plantvillage-dataset</t>
   </si>
 </sst>
 </file>
@@ -199,7 +222,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -223,6 +246,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -624,22 +650,38 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="3"/>
+    <row r="3" spans="1:8" ht="145" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="8">
+        <v>45962</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.96220000000000006</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="8"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="E4" s="9"/>
       <c r="F4" s="3"/>
       <c r="G4" s="6"/>
       <c r="H4" s="3"/>
@@ -809,6 +851,8 @@
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{09735EA5-C75B-F04B-B26F-BF9F1871FC01}"/>
     <hyperlink ref="D2" r:id="rId2" xr:uid="{25903024-71CD-EE41-BCF3-BBBC4ADE36AB}"/>
+    <hyperlink ref="G3" r:id="rId3" xr:uid="{7CE13F02-9E82-E34A-8BD0-25AB845DCA06}"/>
+    <hyperlink ref="D3" r:id="rId4" xr:uid="{ABBB0EA7-666F-B84B-B4CE-A92FB8610438}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
